--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2021_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2021_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 19:47</t>
+    <t xml:space="preserve">2026-09-09 22:34</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2021_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2021_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:34</t>
+    <t xml:space="preserve">2026-09-12 19:50</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2021_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2021_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 19:50</t>
+    <t xml:space="preserve">2026-09-24 00:29</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2021_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2021_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:29</t>
+    <t xml:space="preserve">2026-09-27 23:11</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -637,7 +637,7 @@
         <v>2021</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>24.47</v>
+        <v>244.66</v>
       </c>
     </row>
     <row r="3">
@@ -654,7 +654,7 @@
         <v>2021</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>4.33</v>
+        <v>43.31</v>
       </c>
     </row>
     <row r="4">
@@ -671,7 +671,7 @@
         <v>2021</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>2.11</v>
+        <v>21.09</v>
       </c>
     </row>
     <row r="5">
@@ -688,7 +688,7 @@
         <v>2021</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>1.85</v>
+        <v>18.48</v>
       </c>
     </row>
     <row r="6">
@@ -705,7 +705,7 @@
         <v>2021</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>1.75</v>
+        <v>17.53</v>
       </c>
     </row>
     <row r="7">
@@ -722,7 +722,7 @@
         <v>2021</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>1.08</v>
+        <v>10.82</v>
       </c>
     </row>
     <row r="8">
@@ -739,7 +739,7 @@
         <v>2021</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1.01</v>
+        <v>10.08</v>
       </c>
     </row>
     <row r="9">
@@ -756,7 +756,7 @@
         <v>2021</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0.75</v>
+        <v>7.51</v>
       </c>
     </row>
     <row r="10">
@@ -773,7 +773,7 @@
         <v>2021</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0.43</v>
+        <v>4.32</v>
       </c>
     </row>
     <row r="11">
@@ -790,7 +790,7 @@
         <v>2021</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>0.28</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="12">
@@ -807,7 +807,7 @@
         <v>2021</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>0.22</v>
+        <v>2.23</v>
       </c>
     </row>
     <row r="13">
@@ -824,7 +824,7 @@
         <v>2021</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.18</v>
+        <v>1.83</v>
       </c>
     </row>
     <row r="14">
@@ -841,7 +841,7 @@
         <v>2021</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0.16</v>
+        <v>1.59</v>
       </c>
     </row>
     <row r="15">
@@ -858,7 +858,7 @@
         <v>2021</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>0.02</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="16">
@@ -875,7 +875,7 @@
         <v>2021</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>-0.23</v>
+        <v>-2.34</v>
       </c>
     </row>
     <row r="17">
@@ -892,7 +892,7 @@
         <v>2021</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>-0.3</v>
+        <v>-3.05</v>
       </c>
     </row>
     <row r="18">
@@ -909,7 +909,7 @@
         <v>2021</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>-0.51</v>
+        <v>-5.09</v>
       </c>
     </row>
     <row r="19">
@@ -926,7 +926,7 @@
         <v>2021</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>-0.8</v>
+        <v>-8.01</v>
       </c>
     </row>
     <row r="20">
@@ -943,7 +943,7 @@
         <v>2021</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>-0.82</v>
+        <v>-8.17</v>
       </c>
     </row>
     <row r="21">
@@ -960,7 +960,7 @@
         <v>2021</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>-0.86</v>
+        <v>-8.64</v>
       </c>
     </row>
     <row r="22">
@@ -977,7 +977,7 @@
         <v>2021</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>-0.96</v>
+        <v>-9.65</v>
       </c>
     </row>
     <row r="23">
@@ -994,7 +994,7 @@
         <v>2021</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>-1.07</v>
+        <v>-10.66</v>
       </c>
     </row>
     <row r="24">
@@ -1011,7 +1011,7 @@
         <v>2021</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>-1.16</v>
+        <v>-11.64</v>
       </c>
     </row>
     <row r="25">
@@ -1028,7 +1028,7 @@
         <v>2021</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>-1.26</v>
+        <v>-12.62</v>
       </c>
     </row>
     <row r="26">
@@ -1045,7 +1045,7 @@
         <v>2021</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>-1.49</v>
+        <v>-14.93</v>
       </c>
     </row>
     <row r="27">
@@ -1062,7 +1062,7 @@
         <v>2021</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>-1.59</v>
+        <v>-15.88</v>
       </c>
     </row>
     <row r="28">
@@ -1079,7 +1079,7 @@
         <v>2021</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>-1.63</v>
+        <v>-16.32</v>
       </c>
     </row>
     <row r="29">
@@ -1096,7 +1096,7 @@
         <v>2021</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>-1.68</v>
+        <v>-16.8</v>
       </c>
     </row>
     <row r="30">
@@ -1113,7 +1113,7 @@
         <v>2021</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>-1.7</v>
+        <v>-16.98</v>
       </c>
     </row>
     <row r="31">
@@ -1130,7 +1130,7 @@
         <v>2021</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>-1.78</v>
+        <v>-17.84</v>
       </c>
     </row>
     <row r="32">
@@ -1147,7 +1147,7 @@
         <v>2021</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>-1.82</v>
+        <v>-18.23</v>
       </c>
     </row>
     <row r="33">
@@ -1164,7 +1164,7 @@
         <v>2021</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>-1.9</v>
+        <v>-19.02</v>
       </c>
     </row>
     <row r="34">
@@ -1181,7 +1181,7 @@
         <v>2021</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>-1.96</v>
+        <v>-19.59</v>
       </c>
     </row>
     <row r="35">
@@ -1198,7 +1198,7 @@
         <v>2021</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>-1.97</v>
+        <v>-19.69</v>
       </c>
     </row>
     <row r="36">
@@ -1215,7 +1215,7 @@
         <v>2021</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>-2.02</v>
+        <v>-20.25</v>
       </c>
     </row>
     <row r="37">
@@ -1232,7 +1232,7 @@
         <v>2021</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>-2.04</v>
+        <v>-20.38</v>
       </c>
     </row>
     <row r="38">
@@ -1249,7 +1249,7 @@
         <v>2021</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>-2.12</v>
+        <v>-21.22</v>
       </c>
     </row>
     <row r="39">
@@ -1266,7 +1266,7 @@
         <v>2021</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>-2.15</v>
+        <v>-21.51</v>
       </c>
     </row>
     <row r="40">
@@ -1283,7 +1283,7 @@
         <v>2021</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>-2.16</v>
+        <v>-21.65</v>
       </c>
     </row>
     <row r="41">
@@ -1300,7 +1300,7 @@
         <v>2021</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>-2.29</v>
+        <v>-22.88</v>
       </c>
     </row>
     <row r="42">
@@ -1317,7 +1317,7 @@
         <v>2021</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>-2.3</v>
+        <v>-22.98</v>
       </c>
     </row>
     <row r="43">
@@ -1334,7 +1334,7 @@
         <v>2021</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>-2.39</v>
+        <v>-23.91</v>
       </c>
     </row>
     <row r="44">
@@ -1351,7 +1351,7 @@
         <v>2021</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>-2.53</v>
+        <v>-25.33</v>
       </c>
     </row>
     <row r="45">
@@ -1368,7 +1368,7 @@
         <v>2021</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>-2.75</v>
+        <v>-27.46</v>
       </c>
     </row>
     <row r="46">
@@ -1385,7 +1385,7 @@
         <v>2021</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>-2.84</v>
+        <v>-28.42</v>
       </c>
     </row>
     <row r="47">
@@ -1402,7 +1402,7 @@
         <v>2021</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>-3.33</v>
+        <v>-33.33</v>
       </c>
     </row>
     <row r="48">
@@ -1419,7 +1419,7 @@
         <v>2021</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>-3.53</v>
+        <v>-35.32</v>
       </c>
     </row>
     <row r="49">
@@ -1436,7 +1436,7 @@
         <v>2021</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>-3.9</v>
+        <v>-39.03</v>
       </c>
     </row>
     <row r="50">
@@ -1453,7 +1453,7 @@
         <v>2021</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>-4.01</v>
+        <v>-40.05</v>
       </c>
     </row>
     <row r="51">
@@ -1470,7 +1470,7 @@
         <v>2021</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>-4.74</v>
+        <v>-47.35</v>
       </c>
     </row>
     <row r="52">
@@ -1487,7 +1487,7 @@
         <v>2021</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>-5.85</v>
+        <v>-58.5</v>
       </c>
     </row>
     <row r="53">
@@ -1504,7 +1504,7 @@
         <v>2021</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>-18.18</v>
+        <v>-181.77</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2021_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2021_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 23:11</t>
+    <t xml:space="preserve">2026-10-01 20:57</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2021_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2021_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 20:57</t>
+    <t xml:space="preserve">2026-10-02 13:33</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2021_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2021_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:33</t>
+    <t xml:space="preserve">2026-10-05 08:23</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
